--- a/E/HNM03S.xlsx
+++ b/E/HNM03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="390">
   <si>
     <t/>
   </si>
@@ -43,13 +43,22 @@
     <t>RT</t>
   </si>
   <si>
+    <t>20143373</t>
+  </si>
+  <si>
+    <t>IDM KSET HNDK PRMIUM</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>20071123</t>
   </si>
   <si>
     <t>IDM JAS HUJAN SETLN</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>20140873</t>
@@ -58,7 +67,436 @@
     <t>IDM JAS HJ.DISP STLN</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10014035</t>
+  </si>
+  <si>
+    <t>BAGUS SK.LANTAI20920</t>
+  </si>
+  <si>
+    <t>10014036</t>
+  </si>
+  <si>
+    <t>BAGUS SKT.BAJU 20930</t>
+  </si>
+  <si>
+    <t>10006200</t>
+  </si>
+  <si>
+    <t>BAGUS SHOE BRSH 3354</t>
+  </si>
+  <si>
+    <t>20090053</t>
+  </si>
+  <si>
+    <t>BAGUS KAIN LAP SBGNA</t>
+  </si>
+  <si>
+    <t>20030983</t>
+  </si>
+  <si>
+    <t>IDM SERBET HANDUK</t>
+  </si>
+  <si>
+    <t>20038032</t>
+  </si>
+  <si>
+    <t>IDM KAIN LAP PEL</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20085916</t>
+  </si>
+  <si>
+    <t>IDM FOOD SVR 2'S 750</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20121395</t>
+  </si>
+  <si>
+    <t>KIIP RCTANGLR 10S 1L</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20092994</t>
+  </si>
+  <si>
+    <t>IDM CLING WRAP 30X30</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20062464</t>
+  </si>
+  <si>
+    <t>IDM TSK GIGI TRAVEL</t>
+  </si>
+  <si>
+    <t>20038650</t>
+  </si>
+  <si>
+    <t>IDM TUSUK GIGI 200'S</t>
+  </si>
+  <si>
+    <t>20026412</t>
+  </si>
+  <si>
+    <t>INDOMARET LAP MOTOR</t>
+  </si>
+  <si>
+    <t>20026410</t>
+  </si>
+  <si>
+    <t>INDOMARET LAP MOBIL</t>
+  </si>
+  <si>
+    <t>20036334</t>
+  </si>
+  <si>
+    <t>KEN/M MTR WASH SPNG</t>
+  </si>
+  <si>
+    <t>20075589</t>
+  </si>
+  <si>
+    <t>IDM LILIN PUTIH 8'S</t>
+  </si>
+  <si>
+    <t>20072837</t>
+  </si>
+  <si>
+    <t>IDM LILIN ULTAH 12'S</t>
+  </si>
+  <si>
+    <t>20142226</t>
+  </si>
+  <si>
+    <t>IDM KTG SMPH 44X60CM</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20084539</t>
+  </si>
+  <si>
+    <t>KRSBOW GLOVE LATEX</t>
+  </si>
+  <si>
+    <t>20128556</t>
+  </si>
+  <si>
+    <t>IDM PLSTK KLIP 15X10</t>
+  </si>
+  <si>
+    <t>20128557</t>
+  </si>
+  <si>
+    <t>IDM PLSTK KLIP 25X16</t>
+  </si>
+  <si>
+    <t>20082114</t>
+  </si>
+  <si>
+    <t>IDM PLSTK HDPE 15X30</t>
+  </si>
+  <si>
+    <t>20082115</t>
+  </si>
+  <si>
+    <t>IDM PLSTK HDPE 20X35</t>
+  </si>
+  <si>
+    <t>20086810</t>
+  </si>
+  <si>
+    <t>IDM LAP SERBAGUNA</t>
+  </si>
+  <si>
+    <t>20098808</t>
+  </si>
+  <si>
+    <t>BAGUS SRG TGN PLS100</t>
+  </si>
+  <si>
+    <t>20141993</t>
+  </si>
+  <si>
+    <t>LARISST SCRUB SPONGE</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20044863</t>
+  </si>
+  <si>
+    <t>IDM SABUT STNLSS 2'S</t>
+  </si>
+  <si>
+    <t>20139062</t>
+  </si>
+  <si>
+    <t>LARISST SABUT CUCI2S</t>
+  </si>
+  <si>
+    <t>10003530</t>
+  </si>
+  <si>
+    <t>S/B TOUGH CLN SCRB</t>
+  </si>
+  <si>
+    <t>20053561</t>
+  </si>
+  <si>
+    <t>SB EASY CLN SCRB SPG</t>
+  </si>
+  <si>
+    <t>20113117</t>
+  </si>
+  <si>
+    <t>SC.BRITE SBT.JRG M60</t>
+  </si>
+  <si>
+    <t>20129462</t>
+  </si>
+  <si>
+    <t>IDM SPGE MND LG PUFF</t>
+  </si>
+  <si>
+    <t>20033662</t>
+  </si>
+  <si>
+    <t>IDM SPONGE MANDI PCK</t>
+  </si>
+  <si>
+    <t>20133214</t>
+  </si>
+  <si>
+    <t>NXCARE BBL SHWR PUFF</t>
+  </si>
+  <si>
+    <t>20131331</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F CLWV TD10</t>
+  </si>
+  <si>
+    <t>20131332</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F SKR LMI10</t>
+  </si>
+  <si>
+    <t>20080042</t>
+  </si>
+  <si>
+    <t>BYFRSH HANG'N GO CRV</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20117814</t>
+  </si>
+  <si>
+    <t>BYFRSH H 'N GO SKR/B</t>
+  </si>
+  <si>
+    <t>20101038</t>
+  </si>
+  <si>
+    <t>BYFRSH HANG'N GO LIM</t>
+  </si>
+  <si>
+    <t>20117815</t>
+  </si>
+  <si>
+    <t>BYFRSH H 'N GO D/ICE</t>
+  </si>
+  <si>
+    <t>20048540</t>
+  </si>
+  <si>
+    <t>STELLA DAILY/F ORG/B</t>
+  </si>
+  <si>
+    <t>20055262</t>
+  </si>
+  <si>
+    <t>STELLA DAILY/F DRM 7</t>
+  </si>
+  <si>
+    <t>20048539</t>
+  </si>
+  <si>
+    <t>STELLA DAILY/F RED/K</t>
+  </si>
+  <si>
+    <t>20052690</t>
+  </si>
+  <si>
+    <t>AMBI PUR LVDR/C 2ML</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20130339</t>
+  </si>
+  <si>
+    <t>CLFORNIA A/F NEWPORT</t>
+  </si>
+  <si>
+    <t>20130343</t>
+  </si>
+  <si>
+    <t>CLFORNIA A/F STRWBRY</t>
+  </si>
+  <si>
+    <t>20138691</t>
+  </si>
+  <si>
+    <t>STELLA CAR HANG JASM</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20138849</t>
+  </si>
+  <si>
+    <t>AIRPRO ESS FRUITY 9</t>
+  </si>
+  <si>
+    <t>20138690</t>
+  </si>
+  <si>
+    <t>STELLA CAR HANG AQUA</t>
+  </si>
+  <si>
+    <t>20052689</t>
+  </si>
+  <si>
+    <t>AMBI PUR SKY/BR 2ML</t>
+  </si>
+  <si>
+    <t>20111567</t>
+  </si>
+  <si>
+    <t>KAGUMI D.SCNT COFFEE</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20111568</t>
+  </si>
+  <si>
+    <t>KAGUMI D.SCNT T.MNGO</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20132836</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F OCEAN 9ML</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>10005473</t>
+  </si>
+  <si>
+    <t>KIT WASH&amp;GLOW PCH720</t>
+  </si>
+  <si>
+    <t>20130417</t>
+  </si>
+  <si>
+    <t>GLO WSH&amp;SHN SHMPO700</t>
+  </si>
+  <si>
+    <t>10028422</t>
+  </si>
+  <si>
+    <t>KIT WIPER FLD PCH400</t>
+  </si>
+  <si>
+    <t>20001713</t>
+  </si>
+  <si>
+    <t>KIT BLACK MGC GEL180</t>
+  </si>
+  <si>
+    <t>20109707</t>
+  </si>
+  <si>
+    <t>KIT WATERLESS BTL500</t>
+  </si>
+  <si>
+    <t>20090436</t>
+  </si>
+  <si>
+    <t>KIT DETAILER SPRY200</t>
+  </si>
+  <si>
+    <t>20121376</t>
+  </si>
+  <si>
+    <t>KIT MOTOR B TO B 115</t>
+  </si>
+  <si>
+    <t>20013832</t>
+  </si>
+  <si>
+    <t>KIT MOTOR MLTGUNA100</t>
+  </si>
+  <si>
+    <t>20037676</t>
+  </si>
+  <si>
+    <t>KIT MTR CHN.LUBE 110</t>
+  </si>
+  <si>
+    <t>10016210</t>
+  </si>
+  <si>
+    <t>AMBI PUR VAN.BQT 7.5</t>
+  </si>
+  <si>
+    <t>10016209</t>
+  </si>
+  <si>
+    <t>AMBI/P C/FR.AQUA 7.5</t>
+  </si>
+  <si>
+    <t>20016897</t>
+  </si>
+  <si>
+    <t>GLADE CAR FRSH APL70</t>
+  </si>
+  <si>
+    <t>20124786</t>
+  </si>
+  <si>
+    <t>BAYFRESH CPUCCINO 70</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>20039156</t>
@@ -67,387 +505,6 @@
     <t>IDM J/HJN DISP DWSA</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10014035</t>
-  </si>
-  <si>
-    <t>BAGUS SK.LANTAI20920</t>
-  </si>
-  <si>
-    <t>10014036</t>
-  </si>
-  <si>
-    <t>BAGUS SKT.BAJU 20930</t>
-  </si>
-  <si>
-    <t>10006200</t>
-  </si>
-  <si>
-    <t>BAGUS SHOE BRSH 3354</t>
-  </si>
-  <si>
-    <t>20090053</t>
-  </si>
-  <si>
-    <t>BAGUS KAIN LAP SBGNA</t>
-  </si>
-  <si>
-    <t>20030983</t>
-  </si>
-  <si>
-    <t>IDM SERBET HANDUK</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20038032</t>
-  </si>
-  <si>
-    <t>IDM KAIN LAP PEL</t>
-  </si>
-  <si>
-    <t>20085916</t>
-  </si>
-  <si>
-    <t>IDM FOOD SVR 2'S 750</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20121395</t>
-  </si>
-  <si>
-    <t>KIIP RCTANGLR 10S 1L</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20092994</t>
-  </si>
-  <si>
-    <t>IDM CLING WRAP 30X30</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20062464</t>
-  </si>
-  <si>
-    <t>IDM TSK GIGI TRAVEL</t>
-  </si>
-  <si>
-    <t>20038650</t>
-  </si>
-  <si>
-    <t>IDM TUSUK GIGI 200'S</t>
-  </si>
-  <si>
-    <t>20026412</t>
-  </si>
-  <si>
-    <t>INDOMARET LAP MOTOR</t>
-  </si>
-  <si>
-    <t>20026410</t>
-  </si>
-  <si>
-    <t>INDOMARET LAP MOBIL</t>
-  </si>
-  <si>
-    <t>20036334</t>
-  </si>
-  <si>
-    <t>KEN/M MTR WASH SPNG</t>
-  </si>
-  <si>
-    <t>20075589</t>
-  </si>
-  <si>
-    <t>IDM LILIN PUTIH 8'S</t>
-  </si>
-  <si>
-    <t>20072837</t>
-  </si>
-  <si>
-    <t>IDM LILIN ULTAH 12'S</t>
-  </si>
-  <si>
-    <t>20142226</t>
-  </si>
-  <si>
-    <t>IDM KTG SMPH 44X60CM</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20084539</t>
-  </si>
-  <si>
-    <t>KRSBOW GLOVE LATEX</t>
-  </si>
-  <si>
-    <t>20128556</t>
-  </si>
-  <si>
-    <t>IDM PLSTK KLIP 15X10</t>
-  </si>
-  <si>
-    <t>20128557</t>
-  </si>
-  <si>
-    <t>IDM PLSTK KLIP 25X16</t>
-  </si>
-  <si>
-    <t>20082114</t>
-  </si>
-  <si>
-    <t>IDM PLSTK HDPE 15X30</t>
-  </si>
-  <si>
-    <t>20082115</t>
-  </si>
-  <si>
-    <t>IDM PLSTK HDPE 20X35</t>
-  </si>
-  <si>
-    <t>20086810</t>
-  </si>
-  <si>
-    <t>IDM LAP SERBAGUNA</t>
-  </si>
-  <si>
-    <t>20098808</t>
-  </si>
-  <si>
-    <t>BAGUS SRG TGN PLS100</t>
-  </si>
-  <si>
-    <t>20141993</t>
-  </si>
-  <si>
-    <t>LARISST SCRUB SPONGE</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20044863</t>
-  </si>
-  <si>
-    <t>IDM SABUT STNLSS 2'S</t>
-  </si>
-  <si>
-    <t>20139062</t>
-  </si>
-  <si>
-    <t>LARISST SABUT CUCI2S</t>
-  </si>
-  <si>
-    <t>10003530</t>
-  </si>
-  <si>
-    <t>S/B TOUGH CLN SCRB</t>
-  </si>
-  <si>
-    <t>20053561</t>
-  </si>
-  <si>
-    <t>SB EASY CLN SCRB SPG</t>
-  </si>
-  <si>
-    <t>20113117</t>
-  </si>
-  <si>
-    <t>SC.BRITE SBT.JRG M60</t>
-  </si>
-  <si>
-    <t>20129462</t>
-  </si>
-  <si>
-    <t>IDM SPGE MND LG PUFF</t>
-  </si>
-  <si>
-    <t>20033662</t>
-  </si>
-  <si>
-    <t>IDM SPONGE MANDI PCK</t>
-  </si>
-  <si>
-    <t>20133214</t>
-  </si>
-  <si>
-    <t>NXCARE BBL SHWR PUFF</t>
-  </si>
-  <si>
-    <t>20131332</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F SKR LMI10</t>
-  </si>
-  <si>
-    <t>20080042</t>
-  </si>
-  <si>
-    <t>BYFRSH HANG'N GO CRV</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20101038</t>
-  </si>
-  <si>
-    <t>BYFRSH HANG'N GO LIM</t>
-  </si>
-  <si>
-    <t>20048540</t>
-  </si>
-  <si>
-    <t>STELLA DAILY/F ORG/B</t>
-  </si>
-  <si>
-    <t>20048539</t>
-  </si>
-  <si>
-    <t>STELLA DAILY/F RED/K</t>
-  </si>
-  <si>
-    <t>20130343</t>
-  </si>
-  <si>
-    <t>CLFORNIA A/F STRWBRY</t>
-  </si>
-  <si>
-    <t>20138691</t>
-  </si>
-  <si>
-    <t>STELLA CAR HANG JASM</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20138690</t>
-  </si>
-  <si>
-    <t>STELLA CAR HANG AQUA</t>
-  </si>
-  <si>
-    <t>20052689</t>
-  </si>
-  <si>
-    <t>AMBI PUR SKY/BR 2ML</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20111567</t>
-  </si>
-  <si>
-    <t>KAGUMI D.SCNT COFFEE</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20111568</t>
-  </si>
-  <si>
-    <t>KAGUMI D.SCNT T.MNGO</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20132836</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F OCEAN 9ML</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>10005473</t>
-  </si>
-  <si>
-    <t>KIT WASH&amp;GLOW PCH720</t>
-  </si>
-  <si>
-    <t>20130417</t>
-  </si>
-  <si>
-    <t>GLO WSH&amp;SHN SHMPO700</t>
-  </si>
-  <si>
-    <t>10028422</t>
-  </si>
-  <si>
-    <t>KIT WIPER FLD PCH400</t>
-  </si>
-  <si>
-    <t>20001713</t>
-  </si>
-  <si>
-    <t>KIT BLACK MGC GEL180</t>
-  </si>
-  <si>
-    <t>20109707</t>
-  </si>
-  <si>
-    <t>KIT WATERLESS BTL500</t>
-  </si>
-  <si>
-    <t>20090436</t>
-  </si>
-  <si>
-    <t>KIT DETAILER SPRY200</t>
-  </si>
-  <si>
-    <t>20121376</t>
-  </si>
-  <si>
-    <t>KIT MOTOR B TO B 115</t>
-  </si>
-  <si>
-    <t>20013832</t>
-  </si>
-  <si>
-    <t>KIT MOTOR MLTGUNA100</t>
-  </si>
-  <si>
-    <t>20037676</t>
-  </si>
-  <si>
-    <t>KIT MTR CHN.LUBE 110</t>
-  </si>
-  <si>
-    <t>10016210</t>
-  </si>
-  <si>
-    <t>AMBI PUR VAN.BQT 7.5</t>
-  </si>
-  <si>
-    <t>10016209</t>
-  </si>
-  <si>
-    <t>AMBI/P C/FR.AQUA 7.5</t>
-  </si>
-  <si>
-    <t>20016897</t>
-  </si>
-  <si>
-    <t>GLADE CAR FRSH APL70</t>
-  </si>
-  <si>
     <t>20135615</t>
   </si>
   <si>
@@ -802,9 +859,6 @@
     <t>KRSBW HS/CLM B.FLY2S</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>20135301</t>
   </si>
   <si>
@@ -904,18 +958,18 @@
     <t>HANNOCHS C/D SNC 5W</t>
   </si>
   <si>
+    <t>20134457</t>
+  </si>
+  <si>
+    <t>IN-LITE LED BOX 15W</t>
+  </si>
+  <si>
     <t>20094959</t>
   </si>
   <si>
     <t>IN-LITE LED BOX 9W</t>
   </si>
   <si>
-    <t>20134457</t>
-  </si>
-  <si>
-    <t>IN-LITE LED BOX 15W</t>
-  </si>
-  <si>
     <t>20060010</t>
   </si>
   <si>
@@ -955,40 +1009,22 @@
     <t>16</t>
   </si>
   <si>
-    <t>20131331</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F CLWV TD10</t>
-  </si>
-  <si>
-    <t>20124786</t>
-  </si>
-  <si>
-    <t>BAYFRESH CPUCCINO 70</t>
-  </si>
-  <si>
     <t>20076488</t>
   </si>
   <si>
     <t>IDM SAPU LIDI TABAH</t>
   </si>
   <si>
-    <t>20117814</t>
-  </si>
-  <si>
-    <t>BYFRSH H 'N GO SKR/B</t>
-  </si>
-  <si>
     <t>20071449</t>
   </si>
   <si>
     <t>IDM PAYUNG PJG WRNA</t>
   </si>
   <si>
-    <t>20117815</t>
-  </si>
-  <si>
-    <t>BYFRSH H 'N GO D/ICE</t>
+    <t>20126370</t>
+  </si>
+  <si>
+    <t>COOGER MOP CMO4609</t>
   </si>
   <si>
     <t>20126374</t>
@@ -997,208 +1033,154 @@
     <t>TOILETBRUSH GRAY WHT</t>
   </si>
   <si>
-    <t>20055262</t>
-  </si>
-  <si>
-    <t>STELLA DAILY/F DRM 7</t>
-  </si>
-  <si>
     <t>20035266</t>
   </si>
   <si>
     <t>INDOMARET PEL REFILL</t>
   </si>
   <si>
-    <t>20052690</t>
-  </si>
-  <si>
-    <t>AMBI PUR LVDR/C 2ML</t>
-  </si>
-  <si>
     <t>20032453</t>
   </si>
   <si>
     <t>KEN/M STP KNTK F1-4</t>
   </si>
   <si>
-    <t>20130339</t>
-  </si>
-  <si>
-    <t>CLFORNIA A/F NEWPORT</t>
-  </si>
-  <si>
     <t>20126378</t>
   </si>
   <si>
     <t>2PCS DETACBLE BROOM</t>
   </si>
   <si>
-    <t>20138849</t>
-  </si>
-  <si>
-    <t>AIRPRO ESS FRUITY 9</t>
+    <t>20037222</t>
+  </si>
+  <si>
+    <t>KEN/M RKT NYM+SNTR B</t>
+  </si>
+  <si>
+    <t>20011832</t>
+  </si>
+  <si>
+    <t>KEN/M REG+MTR PROTCN</t>
+  </si>
+  <si>
+    <t>20053613</t>
+  </si>
+  <si>
+    <t>IDM TALI TAMBANG 6MM</t>
+  </si>
+  <si>
+    <t>20074350</t>
+  </si>
+  <si>
+    <t>IDM PAYUNG LPT TIGA</t>
+  </si>
+  <si>
+    <t>20026807</t>
+  </si>
+  <si>
+    <t>KEN/M OBENG SET MN6</t>
+  </si>
+  <si>
+    <t>20060033</t>
+  </si>
+  <si>
+    <t>KEN/M WTR FLTR DAIYU</t>
+  </si>
+  <si>
+    <t>10016469</t>
+  </si>
+  <si>
+    <t>KEN/M GAS LIGHTER</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>20126370</t>
-  </si>
-  <si>
-    <t>COOGER MOP CMO4609</t>
-  </si>
-  <si>
-    <t>20037222</t>
-  </si>
-  <si>
-    <t>KEN/M RKT NYM+SNTR B</t>
+    <t>20121040</t>
+  </si>
+  <si>
+    <t>KEN/M KRAN PLSTK PTH</t>
+  </si>
+  <si>
+    <t>20139712</t>
+  </si>
+  <si>
+    <t>IDM SANDAL JPT KRT38</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>20011832</t>
-  </si>
-  <si>
-    <t>KEN/M REG+MTR PROTCN</t>
+    <t>20072320</t>
+  </si>
+  <si>
+    <t>IDM SNDAL PRIA 39-40</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>20053613</t>
-  </si>
-  <si>
-    <t>IDM TALI TAMBANG 6MM</t>
+    <t>20072322</t>
+  </si>
+  <si>
+    <t>IDM SNDAL PRIA 41-42</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>20074350</t>
-  </si>
-  <si>
-    <t>IDM PAYUNG LPT TIGA</t>
+    <t>20093212</t>
+  </si>
+  <si>
+    <t>IDM SANDAL JPT KRT42</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>20026807</t>
-  </si>
-  <si>
-    <t>KEN/M OBENG SET MN6</t>
+    <t>20093211</t>
+  </si>
+  <si>
+    <t>IDM SANDAL JPT KRT40</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>20060033</t>
-  </si>
-  <si>
-    <t>KEN/M WTR FLTR DAIYU</t>
+    <t>20126380</t>
+  </si>
+  <si>
+    <t>30CLIP WINDPROF BSKT</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>10016469</t>
-  </si>
-  <si>
-    <t>KEN/M GAS LIGHTER</t>
+    <t>20118405</t>
+  </si>
+  <si>
+    <t>CLARIS EMBER 12 TTP</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>20121040</t>
-  </si>
-  <si>
-    <t>KEN/M KRAN PLSTK PTH</t>
+    <t>20127779</t>
+  </si>
+  <si>
+    <t>COOGER WALL SOAP W+G</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>20139712</t>
-  </si>
-  <si>
-    <t>IDM SANDAL JPT KRT38</t>
+    <t>20126372</t>
+  </si>
+  <si>
+    <t>DISC MULTI TOOHBRUSH</t>
   </si>
   <si>
     <t>25</t>
-  </si>
-  <si>
-    <t>20072320</t>
-  </si>
-  <si>
-    <t>IDM SNDAL PRIA 39-40</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20072322</t>
-  </si>
-  <si>
-    <t>IDM SNDAL PRIA 41-42</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20093212</t>
-  </si>
-  <si>
-    <t>IDM SANDAL JPT KRT42</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20093211</t>
-  </si>
-  <si>
-    <t>IDM SANDAL JPT KRT40</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20126380</t>
-  </si>
-  <si>
-    <t>30CLIP WINDPROF BSKT</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20118405</t>
-  </si>
-  <si>
-    <t>CLARIS EMBER 12 TTP</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20127779</t>
-  </si>
-  <si>
-    <t>COOGER WALL SOAP W+G</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20126372</t>
-  </si>
-  <si>
-    <t>DISC MULTI TOOHBRUSH</t>
-  </si>
-  <si>
-    <t>33</t>
   </si>
 </sst>
 </file>
@@ -1591,7 +1573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F177"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1678,7 +1660,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1815,7 +1797,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -1823,10 +1805,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1835,7 +1817,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -1995,7 +1977,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>9</v>
@@ -2015,7 +1997,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -2155,7 +2137,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2175,7 +2157,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>9</v>
@@ -2212,7 +2194,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>4</v>
@@ -2232,7 +2214,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>8</v>
@@ -2252,7 +2234,7 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>12</v>
@@ -2272,7 +2254,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>15</v>
@@ -2292,10 +2274,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>9</v>
@@ -2312,10 +2294,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>9</v>
@@ -2332,7 +2314,7 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>34</v>
@@ -2352,7 +2334,7 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>37</v>
@@ -2372,7 +2354,7 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>40</v>
@@ -2392,7 +2374,7 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>4</v>
@@ -2412,33 +2394,33 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2452,13 +2434,13 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2472,13 +2454,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2492,13 +2474,13 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2512,90 +2494,90 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>106</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>106</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="F48" s="1" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>9</v>
@@ -2603,119 +2585,119 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F53" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>9</v>
@@ -2723,19 +2705,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>9</v>
@@ -2743,22 +2725,22 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2775,7 +2757,7 @@
         <v>34</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>9</v>
@@ -2795,7 +2777,7 @@
         <v>34</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>9</v>
@@ -2815,10 +2797,10 @@
         <v>34</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2835,10 +2817,10 @@
         <v>34</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2855,7 +2837,7 @@
         <v>34</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>9</v>
@@ -2872,13 +2854,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2892,13 +2874,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2912,13 +2894,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2932,10 +2914,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>9</v>
@@ -2952,13 +2934,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2972,53 +2954,53 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>157</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>157</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3032,13 +3014,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3052,13 +3034,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3072,13 +3054,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3092,13 +3074,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3112,13 +3094,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3132,13 +3114,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3152,73 +3134,73 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>95</v>
+        <v>176</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>182</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3232,13 +3214,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3252,13 +3234,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3272,13 +3254,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3292,13 +3274,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3312,13 +3294,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3332,13 +3314,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3352,13 +3334,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3372,13 +3354,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3392,610 +3374,610 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>57</v>
@@ -4003,22 +3985,22 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4032,10 +4014,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>9</v>
@@ -4052,13 +4034,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4072,10 +4054,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>9</v>
@@ -4092,13 +4074,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4112,13 +4094,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4132,13 +4114,13 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4152,7 +4134,7 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>37</v>
@@ -4172,13 +4154,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>40</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4192,13 +4174,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>263</v>
+        <v>161</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4212,110 +4194,110 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>9</v>
@@ -4323,39 +4305,39 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>9</v>
@@ -4363,19 +4345,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>9</v>
@@ -4383,22 +4365,22 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4412,13 +4394,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4432,13 +4414,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4452,13 +4434,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>263</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4472,10 +4454,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>284</v>
+        <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4492,190 +4474,190 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>34</v>
+        <v>134</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>37</v>
+        <v>161</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>40</v>
+        <v>302</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4692,13 +4674,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>111</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4712,13 +4694,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4732,10 +4714,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>263</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>9</v>
@@ -4752,10 +4734,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>284</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>9</v>
@@ -4772,30 +4754,30 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>342</v>
+        <v>31</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>313</v>
+        <v>34</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>9</v>
@@ -4803,19 +4785,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>347</v>
+        <v>37</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>9</v>
@@ -4823,19 +4805,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>350</v>
+        <v>40</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>9</v>
@@ -4843,39 +4825,39 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>353</v>
+        <v>128</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>356</v>
+        <v>131</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4883,39 +4865,39 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>359</v>
+        <v>134</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>362</v>
+        <v>161</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>9</v>
@@ -4923,19 +4905,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>365</v>
+        <v>302</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>9</v>
@@ -4943,19 +4925,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>9</v>
@@ -4963,39 +4945,39 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>371</v>
+        <v>331</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5003,19 +4985,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5023,19 +5005,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5043,19 +5025,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5063,39 +5045,39 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>9</v>
@@ -5103,19 +5085,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>9</v>
@@ -5123,21 +5105,41 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F177" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F178" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/E/HNM03S.xlsx
+++ b/E/HNM03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="397">
   <si>
     <t/>
   </si>
@@ -70,6 +70,24 @@
     <t>5</t>
   </si>
   <si>
+    <t>20039156</t>
+  </si>
+  <si>
+    <t>IDM J/HJN DISP DWSA</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20143597</t>
+  </si>
+  <si>
+    <t>IDM JAS HJN PNCO CLN</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>10014035</t>
   </si>
   <si>
@@ -115,18 +133,12 @@
     <t>IDM FOOD SVR 2'S 750</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>20121395</t>
   </si>
   <si>
     <t>KIIP RCTANGLR 10S 1L</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>20092994</t>
   </si>
   <si>
@@ -286,25 +298,103 @@
     <t>NXCARE BBL SHWR PUFF</t>
   </si>
   <si>
+    <t>20131332</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F SKR LMI10</t>
+  </si>
+  <si>
+    <t>20080042</t>
+  </si>
+  <si>
+    <t>BYFRSH HANG'N GO CRV</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20101038</t>
+  </si>
+  <si>
+    <t>BYFRSH HANG'N GO LIM</t>
+  </si>
+  <si>
+    <t>20048540</t>
+  </si>
+  <si>
+    <t>STELLA DAILY/F ORG/B</t>
+  </si>
+  <si>
+    <t>20048539</t>
+  </si>
+  <si>
+    <t>STELLA DAILY/F RED/K</t>
+  </si>
+  <si>
+    <t>20130343</t>
+  </si>
+  <si>
+    <t>CLFORNIA A/F STRWBRY</t>
+  </si>
+  <si>
+    <t>20138691</t>
+  </si>
+  <si>
+    <t>STELLA CAR HANG JASM</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20138690</t>
+  </si>
+  <si>
+    <t>STELLA CAR HANG AQUA</t>
+  </si>
+  <si>
+    <t>20052689</t>
+  </si>
+  <si>
+    <t>AMBI PUR SKY/BR 2ML</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20111567</t>
+  </si>
+  <si>
+    <t>KAGUMI D.SCNT COFFEE</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20111568</t>
+  </si>
+  <si>
+    <t>KAGUMI D.SCNT T.MNGO</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20132836</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F OCEAN 9ML</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>20131331</t>
   </si>
   <si>
     <t>AIRPRO A/F CLWV TD10</t>
   </si>
   <si>
-    <t>20131332</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F SKR LMI10</t>
-  </si>
-  <si>
-    <t>20080042</t>
-  </si>
-  <si>
-    <t>BYFRSH HANG'N GO CRV</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
+    <t>13</t>
   </si>
   <si>
     <t>20117814</t>
@@ -313,10 +403,7 @@
     <t>BYFRSH H 'N GO SKR/B</t>
   </si>
   <si>
-    <t>20101038</t>
-  </si>
-  <si>
-    <t>BYFRSH HANG'N GO LIM</t>
+    <t>14</t>
   </si>
   <si>
     <t>20117815</t>
@@ -325,10 +412,7 @@
     <t>BYFRSH H 'N GO D/ICE</t>
   </si>
   <si>
-    <t>20048540</t>
-  </si>
-  <si>
-    <t>STELLA DAILY/F ORG/B</t>
+    <t>15</t>
   </si>
   <si>
     <t>20055262</t>
@@ -337,10 +421,7 @@
     <t>STELLA DAILY/F DRM 7</t>
   </si>
   <si>
-    <t>20048539</t>
-  </si>
-  <si>
-    <t>STELLA DAILY/F RED/K</t>
+    <t>16</t>
   </si>
   <si>
     <t>20052690</t>
@@ -349,7 +430,7 @@
     <t>AMBI PUR LVDR/C 2ML</t>
   </si>
   <si>
-    <t>PT,(E-3B)</t>
+    <t>17</t>
   </si>
   <si>
     <t>20130339</t>
@@ -358,19 +439,7 @@
     <t>CLFORNIA A/F NEWPORT</t>
   </si>
   <si>
-    <t>20130343</t>
-  </si>
-  <si>
-    <t>CLFORNIA A/F STRWBRY</t>
-  </si>
-  <si>
-    <t>20138691</t>
-  </si>
-  <si>
-    <t>STELLA CAR HANG JASM</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
+    <t>18</t>
   </si>
   <si>
     <t>20138849</t>
@@ -379,43 +448,7 @@
     <t>AIRPRO ESS FRUITY 9</t>
   </si>
   <si>
-    <t>20138690</t>
-  </si>
-  <si>
-    <t>STELLA CAR HANG AQUA</t>
-  </si>
-  <si>
-    <t>20052689</t>
-  </si>
-  <si>
-    <t>AMBI PUR SKY/BR 2ML</t>
-  </si>
-  <si>
-    <t>20111567</t>
-  </si>
-  <si>
-    <t>KAGUMI D.SCNT COFFEE</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20111568</t>
-  </si>
-  <si>
-    <t>KAGUMI D.SCNT T.MNGO</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20132836</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F OCEAN 9ML</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>19</t>
   </si>
   <si>
     <t>10005473</t>
@@ -496,15 +529,6 @@
     <t>BAYFRESH CPUCCINO 70</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20039156</t>
-  </si>
-  <si>
-    <t>IDM J/HJN DISP DWSA</t>
-  </si>
-  <si>
     <t>20135615</t>
   </si>
   <si>
@@ -610,6 +634,123 @@
     <t>WHKAS T/M TNA KNKM70</t>
   </si>
   <si>
+    <t>20121357</t>
+  </si>
+  <si>
+    <t>ME-O OCEAN FISH 80G</t>
+  </si>
+  <si>
+    <t>20096777</t>
+  </si>
+  <si>
+    <t>WHISKAS OCEAN FSH 80</t>
+  </si>
+  <si>
+    <t>20113920</t>
+  </si>
+  <si>
+    <t>ME-O TUNA IN JLY 80G</t>
+  </si>
+  <si>
+    <t>20117626</t>
+  </si>
+  <si>
+    <t>WHKAS T/M CHK TUNA70</t>
+  </si>
+  <si>
+    <t>20031232</t>
+  </si>
+  <si>
+    <t>WHISKAS CF TUNA 80</t>
+  </si>
+  <si>
+    <t>20102393</t>
+  </si>
+  <si>
+    <t>ME-O KTN OCN.FISH 50</t>
+  </si>
+  <si>
+    <t>20140134</t>
+  </si>
+  <si>
+    <t>CUTIES CATZ TUNA 75G</t>
+  </si>
+  <si>
+    <t>20031233</t>
+  </si>
+  <si>
+    <t>WHISKAS CF MAC&amp;SAL80</t>
+  </si>
+  <si>
+    <t>20104599</t>
+  </si>
+  <si>
+    <t>ME-O CRM TRT SLMN 60</t>
+  </si>
+  <si>
+    <t>20128696</t>
+  </si>
+  <si>
+    <t>LIFE CAT KTEN TUNA85</t>
+  </si>
+  <si>
+    <t>20104595</t>
+  </si>
+  <si>
+    <t>ME-O CRM CHKN&amp;LVR 60</t>
+  </si>
+  <si>
+    <t>20126940</t>
+  </si>
+  <si>
+    <t>K/B CAT FD SLMON 120</t>
+  </si>
+  <si>
+    <t>20135980</t>
+  </si>
+  <si>
+    <t>IDM CAT FOOD TUNA 80</t>
+  </si>
+  <si>
+    <t>20128695</t>
+  </si>
+  <si>
+    <t>BIO CREAMY TUNA 4S</t>
+  </si>
+  <si>
+    <t>20135431</t>
+  </si>
+  <si>
+    <t>DELI CRMY TUNA 2X14G</t>
+  </si>
+  <si>
+    <t>20143751</t>
+  </si>
+  <si>
+    <t>MEO TUNA CHKN JLY 80</t>
+  </si>
+  <si>
+    <t>PT,(E-13B)</t>
+  </si>
+  <si>
+    <t>20134232</t>
+  </si>
+  <si>
+    <t>SH CRMY TREATS 4X15G</t>
+  </si>
+  <si>
+    <t>20135432</t>
+  </si>
+  <si>
+    <t>DELI CRM TN&amp;SLMN2X14</t>
+  </si>
+  <si>
+    <t>20143750</t>
+  </si>
+  <si>
+    <t>MEO KTEN TUNA SRDN80</t>
+  </si>
+  <si>
     <t>20121362</t>
   </si>
   <si>
@@ -619,114 +760,12 @@
     <t>RT,(E-9B)</t>
   </si>
   <si>
-    <t>20096777</t>
-  </si>
-  <si>
-    <t>WHISKAS OCEAN FSH 80</t>
-  </si>
-  <si>
-    <t>20117626</t>
-  </si>
-  <si>
-    <t>WHKAS T/M CHK TUNA70</t>
-  </si>
-  <si>
-    <t>20121357</t>
-  </si>
-  <si>
-    <t>ME-O OCEAN FISH 80G</t>
-  </si>
-  <si>
-    <t>20031232</t>
-  </si>
-  <si>
-    <t>WHISKAS CF TUNA 80</t>
-  </si>
-  <si>
-    <t>20113920</t>
-  </si>
-  <si>
-    <t>ME-O TUNA IN JLY 80G</t>
-  </si>
-  <si>
-    <t>20140134</t>
-  </si>
-  <si>
-    <t>CUTIES CATZ TUNA 75G</t>
-  </si>
-  <si>
-    <t>20031233</t>
-  </si>
-  <si>
-    <t>WHISKAS CF MAC&amp;SAL80</t>
-  </si>
-  <si>
     <t>20121808</t>
   </si>
   <si>
     <t>ME-O OTAK2 WF&amp;CS 80G</t>
   </si>
   <si>
-    <t>20128696</t>
-  </si>
-  <si>
-    <t>LIFE CAT KTEN TUNA85</t>
-  </si>
-  <si>
-    <t>20102393</t>
-  </si>
-  <si>
-    <t>ME-O KTN OCN.FISH 50</t>
-  </si>
-  <si>
-    <t>20126940</t>
-  </si>
-  <si>
-    <t>K/B CAT FD SLMON 120</t>
-  </si>
-  <si>
-    <t>20135980</t>
-  </si>
-  <si>
-    <t>IDM CAT FOOD TUNA 80</t>
-  </si>
-  <si>
-    <t>20104599</t>
-  </si>
-  <si>
-    <t>ME-O CRM TRT SLMN 60</t>
-  </si>
-  <si>
-    <t>20128695</t>
-  </si>
-  <si>
-    <t>BIO CREAMY TUNA 4S</t>
-  </si>
-  <si>
-    <t>20135431</t>
-  </si>
-  <si>
-    <t>DELI CRMY TUNA 2X14G</t>
-  </si>
-  <si>
-    <t>20104595</t>
-  </si>
-  <si>
-    <t>ME-O CRM CHKN&amp;LVR 60</t>
-  </si>
-  <si>
-    <t>20134232</t>
-  </si>
-  <si>
-    <t>SH CRMY TREATS 4X15G</t>
-  </si>
-  <si>
-    <t>20135432</t>
-  </si>
-  <si>
-    <t>DELI CRM TN&amp;SLMN2X14</t>
-  </si>
-  <si>
     <t>20098413</t>
   </si>
   <si>
@@ -775,6 +814,54 @@
     <t>IDM DUCKBILL PTIH 4S</t>
   </si>
   <si>
+    <t>20115472</t>
+  </si>
+  <si>
+    <t>IDM MASK 4D HTM 4'S</t>
+  </si>
+  <si>
+    <t>20117862</t>
+  </si>
+  <si>
+    <t>IDM MASKER PCK 5'S</t>
+  </si>
+  <si>
+    <t>20118218</t>
+  </si>
+  <si>
+    <t>IDM MSK SLIM HTM 5S</t>
+  </si>
+  <si>
+    <t>20071626</t>
+  </si>
+  <si>
+    <t>XANDER GEMBOK 50MM</t>
+  </si>
+  <si>
+    <t>20097529</t>
+  </si>
+  <si>
+    <t>KRSBOW PADLOCK 21031</t>
+  </si>
+  <si>
+    <t>20101650</t>
+  </si>
+  <si>
+    <t>B6.ESS BAG HLDR HOOK</t>
+  </si>
+  <si>
+    <t>20038033</t>
+  </si>
+  <si>
+    <t>IDM TALI RAFIA</t>
+  </si>
+  <si>
+    <t>20142274</t>
+  </si>
+  <si>
+    <t>IDM ADHESIVE HOOKS 3</t>
+  </si>
+  <si>
     <t>20131301</t>
   </si>
   <si>
@@ -787,18 +874,6 @@
     <t>IDM MASKER 4D PTH 4S</t>
   </si>
   <si>
-    <t>20115472</t>
-  </si>
-  <si>
-    <t>IDM MASK 4D HTM 4'S</t>
-  </si>
-  <si>
-    <t>20117862</t>
-  </si>
-  <si>
-    <t>IDM MASKER PCK 5'S</t>
-  </si>
-  <si>
     <t>20120506</t>
   </si>
   <si>
@@ -811,48 +886,12 @@
     <t>NXCARE CRBN MASK 2'S</t>
   </si>
   <si>
-    <t>20118218</t>
-  </si>
-  <si>
-    <t>IDM MSK SLIM HTM 5S</t>
-  </si>
-  <si>
-    <t>20071626</t>
-  </si>
-  <si>
-    <t>XANDER GEMBOK 50MM</t>
-  </si>
-  <si>
     <t>20142764</t>
   </si>
   <si>
     <t>IDM MSKR SLIM PTH 5S</t>
   </si>
   <si>
-    <t>20097529</t>
-  </si>
-  <si>
-    <t>KRSBOW PADLOCK 21031</t>
-  </si>
-  <si>
-    <t>20101650</t>
-  </si>
-  <si>
-    <t>B6.ESS BAG HLDR HOOK</t>
-  </si>
-  <si>
-    <t>20038033</t>
-  </si>
-  <si>
-    <t>IDM TALI RAFIA</t>
-  </si>
-  <si>
-    <t>20142274</t>
-  </si>
-  <si>
-    <t>IDM ADHESIVE HOOKS 3</t>
-  </si>
-  <si>
     <t>20126285</t>
   </si>
   <si>
@@ -919,9 +958,6 @@
     <t>PHILIPS LED E27 13WT</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>20123181</t>
   </si>
   <si>
@@ -1006,9 +1042,6 @@
     <t>INDOMARET ALAT PEL</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>20076488</t>
   </si>
   <si>
@@ -1093,9 +1126,6 @@
     <t>KEN/M GAS LIGHTER</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>20121040</t>
   </si>
   <si>
@@ -1108,25 +1138,16 @@
     <t>IDM SANDAL JPT KRT38</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>20072320</t>
   </si>
   <si>
     <t>IDM SNDAL PRIA 39-40</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>20072322</t>
   </si>
   <si>
     <t>IDM SNDAL PRIA 41-42</t>
-  </si>
-  <si>
-    <t>19</t>
   </si>
   <si>
     <t>20093212</t>
@@ -1573,14 +1594,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1714,41 +1735,38 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -1757,7 +1775,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>9</v>
@@ -1765,10 +1783,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1777,7 +1795,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>9</v>
@@ -1785,10 +1803,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1797,18 +1815,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1817,18 +1835,18 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1837,7 +1855,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1860,7 +1878,7 @@
         <v>37</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1877,50 +1895,50 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1937,10 +1955,10 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1957,10 +1975,10 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1977,7 +1995,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>9</v>
@@ -1997,10 +2015,10 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2017,10 +2035,10 @@
         <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2040,15 +2058,15 @@
         <v>37</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -2057,7 +2075,7 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2065,22 +2083,22 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2094,10 +2112,10 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2117,7 +2135,7 @@
         <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -2137,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2157,10 +2175,10 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2177,10 +2195,10 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2194,41 +2212,41 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -2237,10 +2255,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2257,10 +2275,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2277,10 +2295,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2297,7 +2315,7 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>9</v>
@@ -2317,10 +2335,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2340,7 +2358,7 @@
         <v>37</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2357,10 +2375,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2374,13 +2392,13 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2394,13 +2412,13 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2414,33 +2432,33 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2454,13 +2472,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2474,13 +2492,13 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2494,10 +2512,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>9</v>
@@ -2514,10 +2532,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>9</v>
@@ -2534,33 +2552,33 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2574,30 +2592,30 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>9</v>
@@ -2605,119 +2623,119 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>34</v>
+        <v>121</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>119</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>9</v>
@@ -2725,39 +2743,39 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>9</v>
@@ -2765,39 +2783,39 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>145</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>9</v>
@@ -2805,19 +2823,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>9</v>
@@ -2825,19 +2843,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>9</v>
@@ -2845,19 +2863,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>9</v>
@@ -2865,19 +2883,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>9</v>
@@ -2885,16 +2903,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>37</v>
@@ -2905,19 +2923,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>9</v>
@@ -2925,939 +2943,939 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>176</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>97</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>201</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>97</v>
+        <v>239</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>248</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3865,239 +3883,239 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4105,99 +4123,99 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>9</v>
@@ -4205,59 +4223,59 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>9</v>
@@ -4265,19 +4283,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>9</v>
@@ -4285,19 +4303,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>9</v>
@@ -4305,39 +4323,39 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>9</v>
@@ -4345,19 +4363,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>9</v>
@@ -4365,19 +4383,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>302</v>
+        <v>127</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4385,59 +4403,59 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>302</v>
+        <v>127</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>302</v>
+        <v>127</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4445,19 +4463,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4465,79 +4483,79 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>9</v>
@@ -4545,19 +4563,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>9</v>
@@ -4565,19 +4583,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>9</v>
@@ -4585,19 +4603,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>134</v>
+        <v>44</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>9</v>
@@ -4605,99 +4623,99 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>302</v>
+        <v>121</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>331</v>
+        <v>130</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>331</v>
+        <v>130</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>331</v>
+        <v>130</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4705,59 +4723,59 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4765,19 +4783,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>9</v>
@@ -4785,19 +4803,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>9</v>
@@ -4805,39 +4823,39 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>9</v>
@@ -4845,59 +4863,59 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>134</v>
+        <v>44</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>9</v>
@@ -4905,59 +4923,59 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>302</v>
+        <v>121</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>360</v>
+        <v>124</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>331</v>
+        <v>127</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>9</v>
@@ -4965,79 +4983,79 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>365</v>
+        <v>130</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>368</v>
+        <v>133</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>371</v>
+        <v>136</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>374</v>
+        <v>139</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5054,10 +5072,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>377</v>
+        <v>142</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5065,81 +5083,141 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>380</v>
+        <v>145</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E176" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="F176" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E177" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="F177" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="F178" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E178" s="1" t="s">
+      <c r="B179" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="F178" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F181" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/E/HNM03S.xlsx
+++ b/E/HNM03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="397">
   <si>
     <t/>
   </si>
@@ -1744,7 +1744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -1759,6 +1759,9 @@
       </c>
       <c r="E8" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
